--- a/06-játék/csoportok.xlsx
+++ b/06-játék/csoportok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ng210\Documents\webprog\06-játék\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{424C2037-2EBE-4CF9-AA33-74F987C4C3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929C2062-D557-4271-A15F-01FFAF60B2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/06-játék/csoportok.xlsx
+++ b/06-játék/csoportok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ng210\Documents\webprog\06-játék\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929C2062-D557-4271-A15F-01FFAF60B2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209AD227-0B20-4999-854F-25F72883A983}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Patrik</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Frogger</t>
+  </si>
+  <si>
+    <t>Autós</t>
   </si>
 </sst>
 </file>
@@ -490,6 +493,9 @@
       <c r="C5" t="s">
         <v>18</v>
       </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
